--- a/data-manipulation-scripts/sheets-cleanup/sheets/PARTIDA - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PARTIDA - 27_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -28,31 +28,31 @@
     <t>070341173800</t>
   </si>
   <si>
-    <t>IP IRON NXR150 KS 2009 EM DIANTE 173497</t>
+    <t xml:space="preserve">INTERRUPTOR PARTIDA  IRON NXR150 KS 2009 EM DIANTE 173497 </t>
   </si>
   <si>
     <t>7899468003356</t>
   </si>
   <si>
-    <t>IP AUDAX NXR150 2006 A 2009</t>
+    <t>INTERRUPTOR PARTIDA  AUDAX NXR150 2006 A 2009</t>
   </si>
   <si>
     <t>7908253810151</t>
   </si>
   <si>
-    <t>IP TMAC FAZER YS250 2001 A 2015 TM071</t>
+    <t>INTERRUPTOR PARTIDA  TMAC FAZER YS250 2001 A 2015 TM071</t>
   </si>
   <si>
     <t>7895099126358</t>
   </si>
   <si>
-    <t>IP IRON TITAN CG150 2014 A 2021/ FAN160 2016 A 2018 46513</t>
+    <t>INTERRUPTOR PARTIDA IRON TITAN CG150 2014 A 2021/ FAN160 2016 A 2018 46513</t>
   </si>
   <si>
     <t>7909201023128</t>
   </si>
   <si>
-    <t>IP CONDOR XRE190 1104504</t>
+    <t>INTERRUPTOR PARTIDA  CONDOR XRE190 1104504</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -61,232 +61,187 @@
     <t>7899248142749</t>
   </si>
   <si>
-    <t>IP CONDOR CBX250 TWISTER 1103224</t>
+    <t>INTERRUPTOR PARTIDA  CONDOR CBX250 TWISTER 1103224</t>
   </si>
   <si>
     <t>7895099122206</t>
   </si>
   <si>
-    <t>IP IRON YES125 2008 EM DIANTE 27437</t>
+    <t>INTERRUPTOR PARTIDA  IRON YES125 2008 EM DIANTE 27437</t>
   </si>
   <si>
     <t>7898508616365</t>
   </si>
   <si>
-    <t>IP MAGNETRON CB300</t>
-  </si>
-  <si>
-    <t>0000010014899</t>
-  </si>
-  <si>
-    <t>CP RT NXR160001489</t>
-  </si>
-  <si>
-    <t>7908885019984</t>
-  </si>
-  <si>
-    <t>CL RT FAZER150 2016 A 2022/ FACTOR 150 001497</t>
-  </si>
-  <si>
-    <t>7899101751194</t>
-  </si>
-  <si>
-    <t>IF ALLEN FALCON 2006 EM DIANTE 75119</t>
+    <t>INTERRUPTOR PARTIDA  MAGNETRON CB300</t>
   </si>
   <si>
     <t>7908180608227</t>
   </si>
   <si>
-    <t>IP ZOUIL TITAN CG150 2015/ FA160 2016 A 2023</t>
+    <t>INTERRUPTOR PARTIDA ZOUIL TITAN CG150 2015/ FA160 2016 A 2023</t>
   </si>
   <si>
     <t>7908305602222</t>
   </si>
   <si>
-    <t>IP MHX FAN TITAN150 2014 A 2015/ FAN160 RD-43809</t>
+    <t>INTERRUPTOR PARTIDA MHX FAN TITAN150 2014 A 2015/ FAN160 RD-43809</t>
   </si>
   <si>
     <t>7899468003264</t>
   </si>
   <si>
-    <t xml:space="preserve">IP AUDAX XR250 TORNADO 2002 A 2005 </t>
+    <t xml:space="preserve">INTERRUPTOR PARTIDA AUDAX XR250 TORNADO 2002 A 2005 </t>
   </si>
   <si>
     <t>7899248153912</t>
   </si>
   <si>
-    <t>IP CONDOR XR250 TORNADO 2006 A 2008 1103761</t>
+    <t>INTERRUPTOR PARTIDA CONDOR XR250 TORNADO 2006 A 2008 1103761</t>
   </si>
   <si>
     <t>618341657045</t>
   </si>
   <si>
-    <t>IP IRON NXR150 2008/ XR250 TORNADO ATÉ 2005 023572</t>
+    <t>INTERRUPTOR PARTIDA IRON NXR150 2008/ XR250 TORNADO ATÉ 2005 023572</t>
   </si>
   <si>
     <t>7908429152214</t>
   </si>
   <si>
-    <t>IP XILLION PCX150 9798</t>
-  </si>
-  <si>
-    <t>070341176351</t>
-  </si>
-  <si>
-    <t>IB IRON LEAD110 2010 A 2015/ ELITE125 2019 350539</t>
+    <t>INTERRUPTOR PARTIDA XILLION PCX150 9798</t>
   </si>
   <si>
     <t>7908073725574</t>
   </si>
   <si>
-    <t>IP SMARTFOX FAZER250 2006 A 2015</t>
+    <t>INTERRUPTOR PARTIDA SMARTFOX FAZER250 2006 A 2015</t>
   </si>
   <si>
     <t>7777777777</t>
   </si>
   <si>
-    <t>IP DIX YBR125 2009</t>
-  </si>
-  <si>
-    <t>CL RIIE CBX250 TWISTER 2001 A 2008 IP0024</t>
+    <t>INTERRUPTOR PARTIDA DIX YBR125 2009</t>
   </si>
   <si>
     <t>7895099122428</t>
   </si>
   <si>
-    <t>IP IRON YBR125 ATÉ 2008 028353</t>
+    <t>INTERRUPTOR PARTIDA IRON YBR125 ATÉ 2008 028353</t>
   </si>
   <si>
     <t>602883768277</t>
   </si>
   <si>
-    <t>IP IRON NXR160 188979</t>
-  </si>
-  <si>
-    <t>000010014967</t>
-  </si>
-  <si>
-    <t>CL RIIE FAZE250 2005 A 2010 001496</t>
+    <t>INTERRUPTOR PARTIDA IRON NXR160 188979</t>
   </si>
   <si>
     <t>602883768666</t>
   </si>
   <si>
-    <t>IP IRON FAZER YS150 188957</t>
+    <t>INTERRUPTOR PARTIDA IRON FAZER YS150 188957</t>
   </si>
   <si>
     <t>7899641886479</t>
   </si>
   <si>
-    <t>IP VEDAMOTORS YBR125 2002 A 2009 501283</t>
+    <t>INTERRUPTOR PARTIDA VEDAMOTORS YBR125 2002 A 2009 501283</t>
   </si>
   <si>
     <t>7898540623123</t>
   </si>
   <si>
-    <t>IP SCUDE NXR150 2009 10460007</t>
+    <t>INTERRUPTOR PARTIDA SCUDE NXR150 2009 10460007</t>
   </si>
   <si>
     <t>7895099125849</t>
   </si>
   <si>
-    <t>IP IRON CBX250 TWISTER ATÉ 045390</t>
+    <t>INTERRUPTOR PARTIDA IRON CBX250 TWISTER ATÉ 045390</t>
   </si>
   <si>
     <t>602883768284</t>
   </si>
   <si>
-    <t>IP IRON CB250F TWISTER 188381</t>
+    <t>INTERRUPTOR PARTIDA IRON CB250F TWISTER 188381</t>
   </si>
   <si>
     <t>7898540623130</t>
   </si>
   <si>
-    <t>IP SCUD NXR150 2006 A 2008 KS 10460008</t>
+    <t>INTERRUPTOR PARTIDA SCUD NXR150 2006 A 2008 KS 10460008</t>
   </si>
   <si>
     <t>7895099122374</t>
   </si>
   <si>
-    <t>IP IRON NXR150 2009 A 2015 ESD 28348</t>
+    <t>INTERRUPTOR PARTIDA IRON NXR150 2009 A 2015 ESD 28348</t>
   </si>
   <si>
     <t>7898508616761</t>
   </si>
   <si>
-    <t>IP MAGNETRON XRE300 FLEX 2013 A 2015/ XRE300 2010 A 2015 90237110</t>
+    <t>INTERRUPTOR PARTIDA MAGNETRON XRE300 FLEX 2013 A 2015/ XRE300 2010 A 2015 90237110</t>
   </si>
   <si>
     <t>7899761404737</t>
   </si>
   <si>
-    <t>IP MAGNETRON XRE300 2016 A 2018 90237430</t>
+    <t>INTERRUPTOR PARTIDA MAGNETRON XRE300 2016 A 2018 90237430</t>
   </si>
   <si>
     <t>7899651804135</t>
   </si>
   <si>
-    <t>IP SCUD XRE300 10460022</t>
+    <t>INTERRUPTOR PARTIDA SCUD XRE300 10460022</t>
   </si>
   <si>
     <t>7895099122367</t>
   </si>
   <si>
-    <t>IP IRON NXR150 KS 2006 A 2008 28347</t>
+    <t>INTERRUPTOR PARTIDA IRON NXR150 KS 2006 A 2008 28347</t>
   </si>
   <si>
     <t>7899468003363</t>
   </si>
   <si>
-    <t xml:space="preserve">IP TRILHA XRE300 2012 A 2015 </t>
+    <t xml:space="preserve">INTERRUPTOR PARTIDA TRILHA XRE300 2012 A 2015 </t>
   </si>
   <si>
     <t>7895099122459</t>
   </si>
   <si>
-    <t>IP IRON CG TITAN150 2004 A 2008 ES 28356</t>
+    <t>INTERRUPTOR PARTIDA IRON CG TITAN150 2004 A 2008 ES 28356</t>
   </si>
   <si>
     <t>7895099122190</t>
   </si>
   <si>
-    <t>IP IRON YBR125 ATÉ 2008 ED 027442</t>
-  </si>
-  <si>
-    <t>618341656956</t>
-  </si>
-  <si>
-    <t>CL IRON XTZ250 LANDER/ TENERE 2001 A 2015 200541</t>
+    <t>INTERRUPTOR PARTIDA IRON YBR125 ATÉ 2008 ED 027442</t>
   </si>
   <si>
     <t>7908180603352</t>
   </si>
   <si>
-    <t>IP ZOUIL TITAN CG FAN150 2011 A 2013 FLEX</t>
+    <t>INTERRUPTOR PARTIDA ZOUIL TITAN CG FAN150 2011 A 2013 FLEX</t>
   </si>
   <si>
     <t>602883768697</t>
   </si>
   <si>
-    <t>IP IRON YBR125/ FACTOR125 2014 A 2016 188963</t>
+    <t>INTERRUPTOR PARTIDA IRON YBR125/ FACTOR125 2014 A 2016 188963</t>
   </si>
   <si>
     <t>618341657007</t>
   </si>
   <si>
-    <t>IP IRON CG TITAN FAN150-160 2018 A 2023 200530</t>
-  </si>
-  <si>
-    <t>7909201023104</t>
-  </si>
-  <si>
-    <t>CL CONDOR CG TITAN FAN160 1104502</t>
+    <t>INTERRUPTOR PARTIDA IRON CG TITAN FAN150-160 2018 A 2023 200530</t>
   </si>
   <si>
     <t>7895099122213</t>
   </si>
   <si>
-    <t>IP IRON YES125 2005 A 2007/ INTRUDER125</t>
+    <t>INTERRUPTOR PARTIDA IRON YES125 2005 A 2007/ INTRUDER125</t>
   </si>
 </sst>
 </file>
@@ -694,11 +649,9 @@
         <v>22</v>
       </c>
       <c r="C10" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>60.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -710,7 +663,9 @@
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>115.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -720,10 +675,10 @@
         <v>26</v>
       </c>
       <c r="C12" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="2">
-        <v>100.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="13">
@@ -736,7 +691,9 @@
       <c r="C13" s="2">
         <v>1.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -746,11 +703,9 @@
         <v>30</v>
       </c>
       <c r="C14" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>115.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -760,10 +715,10 @@
         <v>32</v>
       </c>
       <c r="C15" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D15" s="2">
-        <v>49.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="16">
@@ -776,9 +731,7 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="2">
-        <v>50.0</v>
-      </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -788,7 +741,7 @@
         <v>36</v>
       </c>
       <c r="C17" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D17" s="3"/>
     </row>
@@ -800,11 +753,9 @@
         <v>38</v>
       </c>
       <c r="C18" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>118.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -828,7 +779,9 @@
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -843,23 +796,23 @@
       <c r="D21" s="3"/>
     </row>
     <row r="22">
-      <c r="A22" s="4"/>
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>60.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
@@ -868,62 +821,60 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
-      <c r="D25" s="2">
-        <v>65.0</v>
-      </c>
+      <c r="D25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D26" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="2">
         <v>1.0</v>
@@ -932,10 +883,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2">
         <v>1.0</v>
@@ -944,22 +895,24 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D30" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2">
         <v>1.0</v>
@@ -968,13 +921,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D32" s="2">
         <v>30.0</v>
@@ -982,22 +935,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34" s="2">
         <v>1.0</v>
@@ -1006,152 +959,100 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D36" s="2">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D37" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D38" s="2">
-        <v>30.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D40" s="2">
-        <v>75.0</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
       <c r="D41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>50.0</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D43" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>60.0</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A46" s="4"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -6832,62 +6733,14 @@
       <c r="C992" s="3"/>
       <c r="D992" s="3"/>
     </row>
-    <row r="993">
-      <c r="A993" s="4"/>
-      <c r="B993" s="3"/>
-      <c r="C993" s="3"/>
-      <c r="D993" s="3"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="4"/>
-      <c r="B994" s="3"/>
-      <c r="C994" s="3"/>
-      <c r="D994" s="3"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="4"/>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
-      <c r="D995" s="3"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="4"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A992">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A992">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
